--- a/Engineering Learning Plan.xlsx
+++ b/Engineering Learning Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3adcba188de36dd1/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F12FD247-2CEE-4E3D-98C3-4A3B560735CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{F12FD247-2CEE-4E3D-98C3-4A3B560735CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE50EDF9-487D-4F08-BAE2-92E6B9BA3B37}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{3B54359A-EE69-4289-9592-1C20E7C1E6FD}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="571">
   <si>
     <t>Unit</t>
   </si>
@@ -1523,6 +1523,222 @@
   </si>
   <si>
     <t>Fault-Aware Autonomous UAS Ecosystem, Integrates:</t>
+  </si>
+  <si>
+    <t>39A</t>
+  </si>
+  <si>
+    <t>Neural Networks for Engineering Systems</t>
+  </si>
+  <si>
+    <t>Learn practical deep learning fundamentals</t>
+  </si>
+  <si>
+    <t>Function approximation, nonlinear modeling</t>
+  </si>
+  <si>
+    <t>MLPs, backpropagation, gradient descent, regularization, train/validation/test splits</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, Jupyter</t>
+  </si>
+  <si>
+    <t>Vehicle Dynamics Surrogate Model</t>
+  </si>
+  <si>
+    <t>Digital twins, model replacement, simulation acceleration</t>
+  </si>
+  <si>
+    <t>Learn how neural networks approximate system behavior</t>
+  </si>
+  <si>
+    <t>Compare prediction errors across operating regions and perform sensitivity analysis</t>
+  </si>
+  <si>
+    <t>AI Performance Report</t>
+  </si>
+  <si>
+    <t>Model predicts dynamics accurately compared to physics simulation</t>
+  </si>
+  <si>
+    <t>39B</t>
+  </si>
+  <si>
+    <t>Computer Vision for Autonomy</t>
+  </si>
+  <si>
+    <t>Learn vision-based autonomy concepts</t>
+  </si>
+  <si>
+    <t>Image processing, perception, classification</t>
+  </si>
+  <si>
+    <t>CNNs, OpenCV, feature extraction, image segmentation, object detection, confusion matrices</t>
+  </si>
+  <si>
+    <t>Python, OpenCV, PyTorch</t>
+  </si>
+  <si>
+    <t>Landing Marker Detection System</t>
+  </si>
+  <si>
+    <t>Vision-aided navigation and perception</t>
+  </si>
+  <si>
+    <t>First exposure to perception stack development</t>
+  </si>
+  <si>
+    <t>Analyze false positives/negatives and perform Pareto failure analysis</t>
+  </si>
+  <si>
+    <t>Detection Evaluation Report</t>
+  </si>
+  <si>
+    <t>Reliable detection under varying conditions</t>
+  </si>
+  <si>
+    <t>39C</t>
+  </si>
+  <si>
+    <t>Reinforcement Learning Deep Dive</t>
+  </si>
+  <si>
+    <t>Learn learning-based control and decision making</t>
+  </si>
+  <si>
+    <t>Sequential decision making</t>
+  </si>
+  <si>
+    <t>MDPs, PPO, DQN, SAC, reward shaping, exploration vs exploitation</t>
+  </si>
+  <si>
+    <t>Python, Stable-Baselines3, PyTorch</t>
+  </si>
+  <si>
+    <t>Advanced RL Navigation Agent</t>
+  </si>
+  <si>
+    <t>Autonomous decision-making</t>
+  </si>
+  <si>
+    <t>Learn where RL is stronger and weaker than classical control</t>
+  </si>
+  <si>
+    <t>Monte Carlo evaluation across randomized environments</t>
+  </si>
+  <si>
+    <t>RL Evaluation Report</t>
+  </si>
+  <si>
+    <t>RL agent performs comparably to classical approaches in defined scenarios</t>
+  </si>
+  <si>
+    <t>39D</t>
+  </si>
+  <si>
+    <t>Multi-Agent AI &amp; Swarming</t>
+  </si>
+  <si>
+    <t>Learn distributed autonomous coordination</t>
+  </si>
+  <si>
+    <t>Cooperative autonomy</t>
+  </si>
+  <si>
+    <t>Consensus algorithms, task allocation, swarm behaviors, decentralized decision making</t>
+  </si>
+  <si>
+    <t>Python, ROS2 (optional)</t>
+  </si>
+  <si>
+    <t>Cooperative Search Mission</t>
+  </si>
+  <si>
+    <t>Swarming, collaborative autonomy, distributed systems</t>
+  </si>
+  <si>
+    <t>Direct relevance to defense autonomy and multi-UAS systems</t>
+  </si>
+  <si>
+    <t>Analyze mission efficiency and communication bottlenecks</t>
+  </si>
+  <si>
+    <t>Swarm Evaluation Report</t>
+  </si>
+  <si>
+    <t>Multiple agents coordinate successfully toward mission goals</t>
+  </si>
+  <si>
+    <t>39E</t>
+  </si>
+  <si>
+    <t>Agentic Autonomy</t>
+  </si>
+  <si>
+    <t>Learn AI-assisted mission planning and reasoning</t>
+  </si>
+  <si>
+    <t>Goal-directed planning and autonomy</t>
+  </si>
+  <si>
+    <t>Agent architectures, planning loops, tool use, mission decomposition, autonomy orchestration</t>
+  </si>
+  <si>
+    <t>Python, LLM APIs (optional), local models</t>
+  </si>
+  <si>
+    <t>Mission Planning Agent</t>
+  </si>
+  <si>
+    <t>Future autonomy architectures and mission management</t>
+  </si>
+  <si>
+    <t>Explore AI-assisted decision support and mission planning</t>
+  </si>
+  <si>
+    <t>Evaluate recommendation quality and planning robustness</t>
+  </si>
+  <si>
+    <t>Agent Architecture Report</t>
+  </si>
+  <si>
+    <t>Agent generates reasonable mission plans and contingencies</t>
+  </si>
+  <si>
+    <t>39F</t>
+  </si>
+  <si>
+    <t>AI Assurance &amp; Evaluation</t>
+  </si>
+  <si>
+    <t>Learn how to evaluate AI systems safely</t>
+  </si>
+  <si>
+    <t>Trustworthiness and verification</t>
+  </si>
+  <si>
+    <t>ROC curves, calibration, uncertainty estimation, confusion matrices, risk analysis, explainability</t>
+  </si>
+  <si>
+    <t>Python, scikit-learn, PyTorch</t>
+  </si>
+  <si>
+    <t>AI Trustworthiness Assessment Framework</t>
+  </si>
+  <si>
+    <t>AI certification, autonomy assurance, safety-critical systems</t>
+  </si>
+  <si>
+    <t>Understand strengths and limitations of AI in autonomy</t>
+  </si>
+  <si>
+    <t>Monte Carlo campaigns, Pareto analysis of AI failure modes, sensitivity analysis</t>
+  </si>
+  <si>
+    <t>AI Safety &amp; Assurance Report</t>
+  </si>
+  <si>
+    <t>Can quantify AI performance, uncertainty, and failure drivers</t>
   </si>
 </sst>
 </file>
@@ -1735,6 +1951,282 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1763,282 +2255,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2053,22 +2269,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA3FA595-0FA0-43EF-9244-90E6527B3D19}" name="Table1" displayName="Table1" ref="A1:M40" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
-  <autoFilter ref="A1:M40" xr:uid="{AA3FA595-0FA0-43EF-9244-90E6527B3D19}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA3FA595-0FA0-43EF-9244-90E6527B3D19}" name="Table1" displayName="Table1" ref="A1:M46" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:M46" xr:uid="{AA3FA595-0FA0-43EF-9244-90E6527B3D19}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{537292FB-75F1-4AEC-8017-A60A3F971FB6}" name="Unit" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{4684766D-57AE-4276-8159-6131C03B2BF2}" name="Focus Area" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{6C162E65-F301-40D3-9CD4-2CCCF27EAC60}" name="Goals" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{18CCC1AF-C377-4DA9-84AB-F0F3C1BDA182}" name="Core Concepts" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{8034025A-C58A-4B68-A5E3-95542BBC6EC3}" name="Key Concepts / Algorithms / Important Topics" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{691786D7-7198-409C-8687-44809857F8C6}" name="Tool Stack" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{60A3B0B7-02E4-4E42-80DF-11FB3C165CF9}" name="Project" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{9C4DDF01-ED84-4541-8E60-7F34D62FF85B}" name="Aero / Autonomy Relevance" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{E7CA8A37-DD4C-461C-AF6F-1235D2900334}" name="AI Integration Opportunity" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{F6DC9111-A538-46BC-9907-C45FDAA1B876}" name="Monte Carlo / Pareto / Operational Analysis Integration" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{972D0B82-5FD3-405A-A086-EC302959BDB7}" name="Engineering Artifact" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{91C1F129-3EDF-4FB8-9215-624916DF947F}" name="Success Criteria" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{7BAF8DB1-A231-479A-A165-0B8F1CE346B1}" name="Duration" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{537292FB-75F1-4AEC-8017-A60A3F971FB6}" name="Unit" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{4684766D-57AE-4276-8159-6131C03B2BF2}" name="Focus Area" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{6C162E65-F301-40D3-9CD4-2CCCF27EAC60}" name="Goals" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{18CCC1AF-C377-4DA9-84AB-F0F3C1BDA182}" name="Core Concepts" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{8034025A-C58A-4B68-A5E3-95542BBC6EC3}" name="Key Concepts / Algorithms / Important Topics" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{691786D7-7198-409C-8687-44809857F8C6}" name="Tool Stack" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{60A3B0B7-02E4-4E42-80DF-11FB3C165CF9}" name="Project" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{9C4DDF01-ED84-4541-8E60-7F34D62FF85B}" name="Aero / Autonomy Relevance" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{E7CA8A37-DD4C-461C-AF6F-1235D2900334}" name="AI Integration Opportunity" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{F6DC9111-A538-46BC-9907-C45FDAA1B876}" name="Monte Carlo / Pareto / Operational Analysis Integration" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{972D0B82-5FD3-405A-A086-EC302959BDB7}" name="Engineering Artifact" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{91C1F129-3EDF-4FB8-9215-624916DF947F}" name="Success Criteria" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{7BAF8DB1-A231-479A-A165-0B8F1CE346B1}" name="Duration" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2668,7 +2884,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C08F8DC-BCEF-4B99-99FC-55457F24AD17}">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="1"/>
@@ -2728,7 +2944,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2892,7 +3108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2933,7 +3149,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3015,7 +3231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3056,7 +3272,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3179,7 +3395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3220,7 +3436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3343,7 +3559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3425,7 +3641,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -3466,7 +3682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -3548,7 +3764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -3589,7 +3805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -3630,7 +3846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -3712,7 +3928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -3753,7 +3969,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -3876,7 +4092,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -4122,7 +4338,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -4163,7 +4379,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -4245,7 +4461,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -4327,10 +4543,257 @@
         <v>477</v>
       </c>
     </row>
+    <row r="41" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A41" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+      <c r="A42" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A43" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A44" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="57" x14ac:dyDescent="0.45">
+      <c r="A45" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A46" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>